--- a/rotten-tomato-scrape/rotten_tomatoes_top50.xlsx
+++ b/rotten-tomato-scrape/rotten_tomatoes_top50.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\scraping\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\scraping\rotten-tomato-scrape\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8896BCA6-DF97-4EB6-B700-93CCB5F8E412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987C025F-BCBA-41D4-A30D-0602E5EDBE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,10 +303,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,156 +617,193 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="139.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
